--- a/Comparison Analysis/Results/Output_monthly_mean_visits-Adjusted.xlsx
+++ b/Comparison Analysis/Results/Output_monthly_mean_visits-Adjusted.xlsx
@@ -387,16 +387,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.674357017819471</v>
+        <v>23.87422088695574</v>
       </c>
       <c r="C2">
-        <v>2.674</v>
+        <v>23.874</v>
       </c>
       <c r="D2">
-        <v>2.64</v>
+        <v>23.6</v>
       </c>
       <c r="E2">
-        <v>2.711</v>
+        <v>24.145</v>
       </c>
     </row>
     <row r="3">
@@ -404,16 +404,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.852902310253938</v>
+        <v>13.94968225233695</v>
       </c>
       <c r="C3">
-        <v>1.853</v>
+        <v>13.95</v>
       </c>
       <c r="D3">
-        <v>1.823</v>
+        <v>13.723</v>
       </c>
       <c r="E3">
-        <v>1.884</v>
+        <v>14.171</v>
       </c>
     </row>
     <row r="4">
@@ -421,16 +421,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.687539499966611</v>
+        <v>11.99473673177914</v>
       </c>
       <c r="C4">
-        <v>1.688</v>
+        <v>11.995</v>
       </c>
       <c r="D4">
-        <v>1.656</v>
+        <v>11.757</v>
       </c>
       <c r="E4">
-        <v>1.719</v>
+        <v>12.225</v>
       </c>
     </row>
     <row r="5">
@@ -438,16 +438,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.387255650084293</v>
+        <v>9.69660610953907</v>
       </c>
       <c r="C5">
-        <v>1.387</v>
+        <v>9.696999999999999</v>
       </c>
       <c r="D5">
-        <v>1.361</v>
+        <v>9.487</v>
       </c>
       <c r="E5">
-        <v>1.414</v>
+        <v>9.904</v>
       </c>
     </row>
     <row r="6">
@@ -455,16 +455,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.27961188165677</v>
+        <v>8.83418335617872</v>
       </c>
       <c r="C6">
-        <v>1.28</v>
+        <v>8.834</v>
       </c>
       <c r="D6">
-        <v>1.253</v>
+        <v>8.581</v>
       </c>
       <c r="E6">
-        <v>1.307</v>
+        <v>9.085000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -472,16 +472,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1.143036928076251</v>
+        <v>7.763692002033302</v>
       </c>
       <c r="C7">
-        <v>1.143</v>
+        <v>7.764</v>
       </c>
       <c r="D7">
-        <v>1.116</v>
+        <v>7.561</v>
       </c>
       <c r="E7">
-        <v>1.169</v>
+        <v>7.968</v>
       </c>
     </row>
     <row r="8">
@@ -489,16 +489,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1.094839347819572</v>
+        <v>7.345521110700448</v>
       </c>
       <c r="C8">
-        <v>1.095</v>
+        <v>7.346</v>
       </c>
       <c r="D8">
-        <v>1.069</v>
+        <v>7.165</v>
       </c>
       <c r="E8">
-        <v>1.12</v>
+        <v>7.524</v>
       </c>
     </row>
     <row r="9">
@@ -506,16 +506,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.9935558948402736</v>
+        <v>6.71291741484819</v>
       </c>
       <c r="C9">
-        <v>0.994</v>
+        <v>6.713</v>
       </c>
       <c r="D9">
-        <v>0.969</v>
+        <v>6.533</v>
       </c>
       <c r="E9">
-        <v>1.019</v>
+        <v>6.893</v>
       </c>
     </row>
     <row r="10">
@@ -523,16 +523,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.9757442813001579</v>
+        <v>6.518851258428912</v>
       </c>
       <c r="C10">
-        <v>0.976</v>
+        <v>6.519</v>
       </c>
       <c r="D10">
-        <v>0.951</v>
+        <v>6.348</v>
       </c>
       <c r="E10">
-        <v>0.998</v>
+        <v>6.685</v>
       </c>
     </row>
     <row r="11">
@@ -540,16 +540,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.9328252104633313</v>
+        <v>6.292896687736284</v>
       </c>
       <c r="C11">
-        <v>0.9330000000000001</v>
+        <v>6.293</v>
       </c>
       <c r="D11">
-        <v>0.909</v>
+        <v>6.122</v>
       </c>
       <c r="E11">
-        <v>0.956</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="12">
@@ -557,16 +557,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.8793888005571251</v>
+        <v>6.003760700087332</v>
       </c>
       <c r="C12">
-        <v>0.879</v>
+        <v>6.004</v>
       </c>
       <c r="D12">
-        <v>0.857</v>
+        <v>5.795</v>
       </c>
       <c r="E12">
-        <v>0.901</v>
+        <v>6.231</v>
       </c>
     </row>
     <row r="13">
@@ -574,16 +574,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.898519822517057</v>
+        <v>6.030449287301271</v>
       </c>
       <c r="C13">
-        <v>0.899</v>
+        <v>6.03</v>
       </c>
       <c r="D13">
-        <v>0.875</v>
+        <v>5.811</v>
       </c>
       <c r="E13">
-        <v>0.922</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="14">
@@ -591,16 +591,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.8310300487940254</v>
+        <v>5.466746731494221</v>
       </c>
       <c r="C14">
-        <v>0.831</v>
+        <v>5.467</v>
       </c>
       <c r="D14">
-        <v>0.8100000000000001</v>
+        <v>5.306</v>
       </c>
       <c r="E14">
-        <v>0.853</v>
+        <v>5.621</v>
       </c>
     </row>
     <row r="15">
@@ -608,16 +608,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.8180433516318508</v>
+        <v>5.420352076236329</v>
       </c>
       <c r="C15">
-        <v>0.8179999999999999</v>
+        <v>5.42</v>
       </c>
       <c r="D15">
-        <v>0.796</v>
+        <v>5.262</v>
       </c>
       <c r="E15">
-        <v>0.84</v>
+        <v>5.579</v>
       </c>
     </row>
     <row r="16">
@@ -625,16 +625,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.7730831133124926</v>
+        <v>5.056691026789582</v>
       </c>
       <c r="C16">
-        <v>0.773</v>
+        <v>5.057</v>
       </c>
       <c r="D16">
-        <v>0.751</v>
+        <v>4.903</v>
       </c>
       <c r="E16">
-        <v>0.795</v>
+        <v>5.219</v>
       </c>
     </row>
     <row r="17">
@@ -642,16 +642,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.7476287582166471</v>
+        <v>4.945919292159871</v>
       </c>
       <c r="C17">
-        <v>0.748</v>
+        <v>4.946</v>
       </c>
       <c r="D17">
-        <v>0.725</v>
+        <v>4.795</v>
       </c>
       <c r="E17">
-        <v>0.769</v>
+        <v>5.102</v>
       </c>
     </row>
     <row r="18">
@@ -659,16 +659,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.7073442557173689</v>
+        <v>4.743211817676086</v>
       </c>
       <c r="C18">
-        <v>0.707</v>
+        <v>4.743</v>
       </c>
       <c r="D18">
-        <v>0.6870000000000001</v>
+        <v>4.592</v>
       </c>
       <c r="E18">
-        <v>0.728</v>
+        <v>4.897</v>
       </c>
     </row>
     <row r="19">
@@ -676,16 +676,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.6936088480057154</v>
+        <v>4.707511466626555</v>
       </c>
       <c r="C19">
-        <v>0.694</v>
+        <v>4.708</v>
       </c>
       <c r="D19">
-        <v>0.672</v>
+        <v>4.548</v>
       </c>
       <c r="E19">
-        <v>0.714</v>
+        <v>4.867</v>
       </c>
     </row>
     <row r="20">
@@ -693,16 +693,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.6852553687363104</v>
+        <v>4.60852821824724</v>
       </c>
       <c r="C20">
-        <v>0.6850000000000001</v>
+        <v>4.609</v>
       </c>
       <c r="D20">
-        <v>0.664</v>
+        <v>4.454</v>
       </c>
       <c r="E20">
-        <v>0.706</v>
+        <v>4.765</v>
       </c>
     </row>
     <row r="21">
@@ -710,16 +710,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.636450384978726</v>
+        <v>4.232442561804106</v>
       </c>
       <c r="C21">
-        <v>0.636</v>
+        <v>4.232</v>
       </c>
       <c r="D21">
-        <v>0.617</v>
+        <v>4.091</v>
       </c>
       <c r="E21">
-        <v>0.657</v>
+        <v>4.373</v>
       </c>
     </row>
     <row r="22">
@@ -727,16 +727,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.651287723813467</v>
+        <v>4.296666644739942</v>
       </c>
       <c r="C22">
-        <v>0.651</v>
+        <v>4.297</v>
       </c>
       <c r="D22">
-        <v>0.631</v>
+        <v>4.143</v>
       </c>
       <c r="E22">
-        <v>0.672</v>
+        <v>4.443</v>
       </c>
     </row>
     <row r="23">
@@ -744,16 +744,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.5926449630372548</v>
+        <v>4.021533774709314</v>
       </c>
       <c r="C23">
-        <v>0.593</v>
+        <v>4.022</v>
       </c>
       <c r="D23">
-        <v>0.573</v>
+        <v>3.878</v>
       </c>
       <c r="E23">
-        <v>0.612</v>
+        <v>4.166</v>
       </c>
     </row>
     <row r="24">
@@ -761,16 +761,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.6012848153243995</v>
+        <v>4.032305336033786</v>
       </c>
       <c r="C24">
-        <v>0.601</v>
+        <v>4.032</v>
       </c>
       <c r="D24">
-        <v>0.582</v>
+        <v>3.888</v>
       </c>
       <c r="E24">
-        <v>0.622</v>
+        <v>4.176</v>
       </c>
     </row>
     <row r="25">
@@ -778,16 +778,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.5573025812967788</v>
+        <v>3.754594132796</v>
       </c>
       <c r="C25">
-        <v>0.5570000000000001</v>
+        <v>3.755</v>
       </c>
       <c r="D25">
-        <v>0.538</v>
+        <v>3.612</v>
       </c>
       <c r="E25">
-        <v>0.577</v>
+        <v>3.9</v>
       </c>
     </row>
   </sheetData>
@@ -832,16 +832,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.424644084437899</v>
+        <v>6.345739471106758</v>
       </c>
       <c r="C2">
-        <v>2.425</v>
+        <v>6.346</v>
       </c>
       <c r="D2">
-        <v>2.393</v>
+        <v>6.277</v>
       </c>
       <c r="E2">
-        <v>2.457</v>
+        <v>6.412</v>
       </c>
     </row>
     <row r="3">
@@ -849,16 +849,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.698299610906693</v>
+        <v>3.966229055007727</v>
       </c>
       <c r="C3">
-        <v>1.698</v>
+        <v>3.966</v>
       </c>
       <c r="D3">
-        <v>1.668</v>
+        <v>3.904</v>
       </c>
       <c r="E3">
-        <v>1.726</v>
+        <v>4.027</v>
       </c>
     </row>
     <row r="4">
@@ -866,16 +866,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.618089844193904</v>
+        <v>3.574799986683723</v>
       </c>
       <c r="C4">
-        <v>1.618</v>
+        <v>3.575</v>
       </c>
       <c r="D4">
-        <v>1.589</v>
+        <v>3.514</v>
       </c>
       <c r="E4">
-        <v>1.648</v>
+        <v>3.637</v>
       </c>
     </row>
     <row r="5">
@@ -883,16 +883,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.396542678730174</v>
+        <v>3.063067176974424</v>
       </c>
       <c r="C5">
-        <v>1.397</v>
+        <v>3.063</v>
       </c>
       <c r="D5">
-        <v>1.369</v>
+        <v>3.007</v>
       </c>
       <c r="E5">
-        <v>1.424</v>
+        <v>3.118</v>
       </c>
     </row>
     <row r="6">
@@ -900,16 +900,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.373625219069111</v>
+        <v>2.981671198749228</v>
       </c>
       <c r="C6">
-        <v>1.374</v>
+        <v>2.982</v>
       </c>
       <c r="D6">
-        <v>1.346</v>
+        <v>2.92</v>
       </c>
       <c r="E6">
-        <v>1.403</v>
+        <v>3.041</v>
       </c>
     </row>
     <row r="7">
@@ -917,16 +917,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1.287491111111973</v>
+        <v>2.765276676617241</v>
       </c>
       <c r="C7">
-        <v>1.287</v>
+        <v>2.765</v>
       </c>
       <c r="D7">
-        <v>1.258</v>
+        <v>2.707</v>
       </c>
       <c r="E7">
-        <v>1.316</v>
+        <v>2.824</v>
       </c>
     </row>
     <row r="8">
@@ -934,16 +934,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1.286933838808514</v>
+        <v>2.744137153245063</v>
       </c>
       <c r="C8">
-        <v>1.287</v>
+        <v>2.744</v>
       </c>
       <c r="D8">
-        <v>1.257</v>
+        <v>2.681</v>
       </c>
       <c r="E8">
-        <v>1.316</v>
+        <v>2.807</v>
       </c>
     </row>
     <row r="9">
@@ -951,16 +951,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1.204708341397586</v>
+        <v>2.575890065657393</v>
       </c>
       <c r="C9">
-        <v>1.205</v>
+        <v>2.576</v>
       </c>
       <c r="D9">
-        <v>1.176</v>
+        <v>2.521</v>
       </c>
       <c r="E9">
-        <v>1.233</v>
+        <v>2.634</v>
       </c>
     </row>
     <row r="10">
@@ -968,16 +968,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1.23201771838178</v>
+        <v>2.611751798678369</v>
       </c>
       <c r="C10">
-        <v>1.232</v>
+        <v>2.612</v>
       </c>
       <c r="D10">
-        <v>1.201</v>
+        <v>2.55</v>
       </c>
       <c r="E10">
-        <v>1.262</v>
+        <v>2.672</v>
       </c>
     </row>
     <row r="11">
@@ -985,16 +985,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1.226833033458292</v>
+        <v>2.610287337107181</v>
       </c>
       <c r="C11">
-        <v>1.227</v>
+        <v>2.61</v>
       </c>
       <c r="D11">
-        <v>1.198</v>
+        <v>2.551</v>
       </c>
       <c r="E11">
-        <v>1.257</v>
+        <v>2.669</v>
       </c>
     </row>
     <row r="12">
@@ -1002,16 +1002,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1.187308927969093</v>
+        <v>2.522680754061051</v>
       </c>
       <c r="C12">
-        <v>1.187</v>
+        <v>2.523</v>
       </c>
       <c r="D12">
-        <v>1.157</v>
+        <v>2.452</v>
       </c>
       <c r="E12">
-        <v>1.217</v>
+        <v>2.594</v>
       </c>
     </row>
     <row r="13">
@@ -1019,16 +1019,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.256220301197073</v>
+        <v>2.657985055884048</v>
       </c>
       <c r="C13">
-        <v>1.256</v>
+        <v>2.658</v>
       </c>
       <c r="D13">
-        <v>1.225</v>
+        <v>2.583</v>
       </c>
       <c r="E13">
-        <v>1.287</v>
+        <v>2.731</v>
       </c>
     </row>
     <row r="14">
@@ -1036,16 +1036,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1.19286512310278</v>
+        <v>2.485104465789995</v>
       </c>
       <c r="C14">
-        <v>1.193</v>
+        <v>2.485</v>
       </c>
       <c r="D14">
-        <v>1.163</v>
+        <v>2.423</v>
       </c>
       <c r="E14">
-        <v>1.222</v>
+        <v>2.546</v>
       </c>
     </row>
     <row r="15">
@@ -1053,16 +1053,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1.212433254441884</v>
+        <v>2.547679504614315</v>
       </c>
       <c r="C15">
-        <v>1.212</v>
+        <v>2.548</v>
       </c>
       <c r="D15">
-        <v>1.181</v>
+        <v>2.486</v>
       </c>
       <c r="E15">
-        <v>1.244</v>
+        <v>2.613</v>
       </c>
     </row>
     <row r="16">
@@ -1070,16 +1070,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>1.186475248391173</v>
+        <v>2.475338392678886</v>
       </c>
       <c r="C16">
-        <v>1.186</v>
+        <v>2.475</v>
       </c>
       <c r="D16">
-        <v>1.155</v>
+        <v>2.407</v>
       </c>
       <c r="E16">
-        <v>1.217</v>
+        <v>2.541</v>
       </c>
     </row>
     <row r="17">
@@ -1087,16 +1087,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>1.176961000780374</v>
+        <v>2.498106228308191</v>
       </c>
       <c r="C17">
-        <v>1.177</v>
+        <v>2.498</v>
       </c>
       <c r="D17">
-        <v>1.144</v>
+        <v>2.434</v>
       </c>
       <c r="E17">
-        <v>1.209</v>
+        <v>2.561</v>
       </c>
     </row>
     <row r="18">
@@ -1104,16 +1104,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1.152793579097383</v>
+        <v>2.432690234967623</v>
       </c>
       <c r="C18">
-        <v>1.153</v>
+        <v>2.433</v>
       </c>
       <c r="D18">
-        <v>1.122</v>
+        <v>2.371</v>
       </c>
       <c r="E18">
-        <v>1.183</v>
+        <v>2.495</v>
       </c>
     </row>
     <row r="19">
@@ -1121,16 +1121,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>1.164114100456143</v>
+        <v>2.480796246637716</v>
       </c>
       <c r="C19">
-        <v>1.164</v>
+        <v>2.481</v>
       </c>
       <c r="D19">
-        <v>1.13</v>
+        <v>2.411</v>
       </c>
       <c r="E19">
-        <v>1.197</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="20">
@@ -1138,16 +1138,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>1.190213340724442</v>
+        <v>2.544150332243091</v>
       </c>
       <c r="C20">
-        <v>1.19</v>
+        <v>2.544</v>
       </c>
       <c r="D20">
-        <v>1.157</v>
+        <v>2.474</v>
       </c>
       <c r="E20">
-        <v>1.223</v>
+        <v>2.615</v>
       </c>
     </row>
     <row r="21">
@@ -1155,16 +1155,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>1.130102745500509</v>
+        <v>2.395865098824824</v>
       </c>
       <c r="C21">
-        <v>1.13</v>
+        <v>2.396</v>
       </c>
       <c r="D21">
-        <v>1.097</v>
+        <v>2.323</v>
       </c>
       <c r="E21">
-        <v>1.162</v>
+        <v>2.464</v>
       </c>
     </row>
     <row r="22">
@@ -1172,16 +1172,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>1.199352204210735</v>
+        <v>2.524061110404501</v>
       </c>
       <c r="C22">
-        <v>1.199</v>
+        <v>2.524</v>
       </c>
       <c r="D22">
-        <v>1.164</v>
+        <v>2.449</v>
       </c>
       <c r="E22">
-        <v>1.234</v>
+        <v>2.598</v>
       </c>
     </row>
     <row r="23">
@@ -1189,16 +1189,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>1.12168980735715</v>
+        <v>2.40745877580982</v>
       </c>
       <c r="C23">
-        <v>1.122</v>
+        <v>2.407</v>
       </c>
       <c r="D23">
-        <v>1.088</v>
+        <v>2.336</v>
       </c>
       <c r="E23">
-        <v>1.155</v>
+        <v>2.478</v>
       </c>
     </row>
     <row r="24">
@@ -1206,16 +1206,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>1.192996735262411</v>
+        <v>2.5024512386382</v>
       </c>
       <c r="C24">
-        <v>1.193</v>
+        <v>2.502</v>
       </c>
       <c r="D24">
-        <v>1.157</v>
+        <v>2.43</v>
       </c>
       <c r="E24">
-        <v>1.228</v>
+        <v>2.576</v>
       </c>
     </row>
     <row r="25">
@@ -1223,16 +1223,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>1.176355852009337</v>
+        <v>2.493331308661943</v>
       </c>
       <c r="C25">
-        <v>1.176</v>
+        <v>2.493</v>
       </c>
       <c r="D25">
-        <v>1.125</v>
+        <v>2.392</v>
       </c>
       <c r="E25">
-        <v>1.228</v>
+        <v>2.599</v>
       </c>
     </row>
   </sheetData>
